--- a/data/por_departamento/San Vicente/establecimientos_salud.xlsx
+++ b/data/por_departamento/San Vicente/establecimientos_salud.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Establecimientos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1277,7 +1277,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>overpass-way-442688120</t>
+          <t>overpass-way-490620150</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>way/442688120</t>
+          <t>way/490620150</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>San Emigdio El Tablón</t>
+          <t>San Cayetano Istepeque</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1322,12 +1322,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>San Emigdio El Tablón</t>
+          <t>San Cayetano Istepeque</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1337,17 +1347,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>13.62483567</t>
+          <t>13.65149183</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-88.86115183</t>
+          <t>-88.80866959</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1357,24 +1367,24 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.8613203 13.624763, -88.8610363 13.624763, -88.8610283 13.6249462, -88.861092 13.6249333, -88.8611181 13.6249273, -88.8611371 13.6249212, -88.8611531 13.6249126, -88.8611982 13.6248843, -88.8612177 13.6248757, -88.8612362 13.6248714, -88.8612623 13.6248679, -88.8612849 13.6248662, -88.8613203 13.624763))</t>
+          <t>POLYGON ((-88.808793 13.6516571, -88.8089002 13.651479, -88.8085339 13.6513234, -88.8084496 13.651512, -88.808793 13.6516571))</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/442688120</t>
+          <t>https://www.openstreetmap.org/way/490620150</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.62483567,-88.86115183</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.65149183,-88.80866959</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>overpass-way-490620150</t>
+          <t>overpass-way-632270864</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1384,12 +1394,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>way/490620150</t>
+          <t>way/632270864</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Periferica San Vicente</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>San Cayetano Istepeque</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1417,11 +1427,6 @@
           <t>Paracentral</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>San Cayetano Istepeque</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>clinic</t>
@@ -1444,17 +1449,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>13.65149183</t>
+          <t>13.64539727</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-88.80866959</t>
+          <t>-88.77790906</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1464,24 +1469,24 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.808793 13.6516571, -88.8089002 13.651479, -88.8085339 13.6513234, -88.8084496 13.651512, -88.808793 13.6516571))</t>
+          <t>POLYGON ((-88.7780875 13.645409, -88.7779788 13.6452372, -88.7777306 13.6453856, -88.7778017 13.6454979, -88.7778393 13.6455573, -88.7780875 13.645409))</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/490620150</t>
+          <t>https://www.openstreetmap.org/way/632270864</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.65149183,-88.80866959</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64539727,-88.77790906</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>overpass-way-632270864</t>
+          <t>overpass-way-742632722</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1491,12 +1496,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>way/632270864</t>
+          <t>way/742632722</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Periferica San Vicente</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1516,7 +1521,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Apastepeque</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1524,6 +1529,16 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Apastepeque</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>clinic</t>
@@ -1546,17 +1561,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>13.64539727</t>
+          <t>13.66954882</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-88.77790906</t>
+          <t>-88.77766136</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1566,24 +1581,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.7780875 13.645409, -88.7779788 13.6452372, -88.7777306 13.6453856, -88.7778017 13.6454979, -88.7778393 13.6455573, -88.7780875 13.645409))</t>
+          <t>POLYGON ((-88.7779254 13.6693919, -88.7779289 13.6693182, -88.7778192 13.669308, -88.7778169 13.669384, -88.7777363 13.6693862, -88.777734 13.6693499, -88.7774468 13.6693511, -88.7774643 13.6697106, -88.7775227 13.6697072, -88.7775227 13.6697447, -88.7775507 13.6697424, -88.777553 13.669815, -88.7777795 13.6698139, -88.7777853 13.669562, -88.7778776 13.6695609, -88.7778717 13.6694781, -88.7777725 13.6694781, -88.7777725 13.6694656, -88.7779242 13.6694645, -88.7779254 13.6693919))</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/632270864</t>
+          <t>https://www.openstreetmap.org/way/742632722</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64539727,-88.77790906</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.66954882,-88.77766136</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>overpass-way-742632722</t>
+          <t>overpass-way-742868753</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1593,7 +1608,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>way/742632722</t>
+          <t>way/742868753</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1618,7 +1633,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Apastepeque</t>
+          <t>San Ildefonso</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1628,12 +1643,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Ministerio de Salud</t>
+          <t>San Ildefonso</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1658,17 +1668,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>13.66954882</t>
+          <t>13.70539435</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-88.77766136</t>
+          <t>-88.56306745</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1678,24 +1688,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.7779254 13.6693919, -88.7779289 13.6693182, -88.7778192 13.669308, -88.7778169 13.669384, -88.7777363 13.6693862, -88.777734 13.6693499, -88.7774468 13.6693511, -88.7774643 13.6697106, -88.7775227 13.6697072, -88.7775227 13.6697447, -88.7775507 13.6697424, -88.777553 13.669815, -88.7777795 13.6698139, -88.7777853 13.669562, -88.7778776 13.6695609, -88.7778717 13.6694781, -88.7777725 13.6694781, -88.7777725 13.6694656, -88.7779242 13.6694645, -88.7779254 13.6693919))</t>
+          <t>POLYGON ((-88.5632849 13.7053618, -88.563296 13.7052271, -88.5631877 13.7052187, -88.5631797 13.7053166, -88.5630759 13.7053085, -88.5630735 13.7053376, -88.5629723 13.7053298, -88.5629774 13.705267, -88.5628924 13.7052604, -88.562872 13.7055113, -88.5632202 13.7055381, -88.5632282 13.7054396, -88.5631923 13.7054368, -88.5631903 13.7054616, -88.5631083 13.7054553, -88.5631123 13.7054071, -88.5631642 13.7054111, -88.563169 13.7053528, -88.5632849 13.7053618))</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/742632722</t>
+          <t>https://www.openstreetmap.org/way/742868753</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.66954882,-88.77766136</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.70539435,-88.56306745</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>overpass-way-742868753</t>
+          <t>overpass-way-1106491198</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1705,12 +1715,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>way/742868753</t>
+          <t>way/1106491198</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>unidad de salud San Lorenzo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1730,7 +1740,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>San Ildefonso</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1738,11 +1748,6 @@
           <t>Paracentral</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>San Ildefonso</t>
-        </is>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>clinic</t>
@@ -1770,12 +1775,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>13.70539435</t>
+          <t>13.70000483</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-88.56306745</t>
+          <t>-88.80684781</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1785,24 +1790,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.5632849 13.7053618, -88.563296 13.7052271, -88.5631877 13.7052187, -88.5631797 13.7053166, -88.5630759 13.7053085, -88.5630735 13.7053376, -88.5629723 13.7053298, -88.5629774 13.705267, -88.5628924 13.7052604, -88.562872 13.7055113, -88.5632202 13.7055381, -88.5632282 13.7054396, -88.5631923 13.7054368, -88.5631903 13.7054616, -88.5631083 13.7054553, -88.5631123 13.7054071, -88.5631642 13.7054111, -88.563169 13.7053528, -88.5632849 13.7053618))</t>
+          <t>POLYGON ((-88.807069 13.6999517, -88.8067377 13.6999282, -88.8067458 13.6999725, -88.8067431 13.7000168, -88.806723 13.7000455, -88.8067029 13.7000481, -88.8067082 13.6999843, -88.8066465 13.6999803, -88.8066412 13.7000494, -88.8066666 13.700052, -88.8066613 13.7001198, -88.8067605 13.7001224, -88.8067645 13.7000768, -88.806731 13.7000768, -88.8067324 13.7000494, -88.8067552 13.7000194, -88.8070609 13.7000416, -88.807065 13.6999986, -88.807069 13.6999517))</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/742868753</t>
+          <t>https://www.openstreetmap.org/way/1106491198</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.70539435,-88.56306745</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.70000483,-88.80684781</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>overpass-way-1106491198</t>
+          <t>overpass-way-1468026498</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1812,22 +1817,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>way/1106491198</t>
+          <t>way/1468026498</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>unidad de salud San Lorenzo</t>
+          <t>Unidad de Salud de Verapaz</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1837,7 +1842,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Verapaz</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1845,19 +1850,24 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6ª Avenida Sur, Verapaz</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Ministerio de Salud</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>clinic</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1867,17 +1877,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>13.70000483</t>
+          <t>13.64315064</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-88.80684781</t>
+          <t>-88.8688962</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -1887,39 +1897,39 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.807069 13.6999517, -88.8067377 13.6999282, -88.8067458 13.6999725, -88.8067431 13.7000168, -88.806723 13.7000455, -88.8067029 13.7000481, -88.8067082 13.6999843, -88.8066465 13.6999803, -88.8066412 13.7000494, -88.8066666 13.700052, -88.8066613 13.7001198, -88.8067605 13.7001224, -88.8067645 13.7000768, -88.806731 13.7000768, -88.8067324 13.7000494, -88.8067552 13.7000194, -88.8070609 13.7000416, -88.807065 13.6999986, -88.807069 13.6999517))</t>
+          <t>POLYGON ((-88.8692004 13.6433853, -88.8692294 13.6433372, -88.8688515 13.6427847, -88.8687972 13.6427757, -88.8685525 13.6429383, -88.868958 13.643546, -88.8692004 13.6433853))</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1106491198</t>
+          <t>https://www.openstreetmap.org/way/1468026498</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.70000483,-88.80684781</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64315064,-88.8688962</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>overpass-way-1468026498</t>
+          <t>hot-way-442688120</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>overpass</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>way/1468026498</t>
+          <t>way/442688120</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Unidad de Salud de Verapaz</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1932,6 +1942,16 @@
           <t>hospital</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Polígono</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>poligono</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>San Vicente</t>
@@ -1939,7 +1959,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Verapaz</t>
+          <t>Guadalupe</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1949,12 +1969,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6ª Avenida Sur, Verapaz</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Ministerio de Salud</t>
+          <t>San Emigdio El Tablón</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1962,11 +1977,6 @@
           <t>hospital</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>Polygon</t>
@@ -1974,17 +1984,17 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>13.64315064</t>
+          <t>13.62483567</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-88.8688962</t>
+          <t>-88.86115183</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -1994,39 +2004,39 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.8692004 13.6433853, -88.8692294 13.6433372, -88.8688515 13.6427847, -88.8687972 13.6427757, -88.8685525 13.6429383, -88.868958 13.643546, -88.8692004 13.6433853))</t>
+          <t>POLYGON ((-88.8613203 13.624763, -88.8610363 13.624763, -88.8610283 13.6249462, -88.861092 13.6249333, -88.8611181 13.6249273, -88.8611371 13.6249212, -88.8611531 13.6249126, -88.8611982 13.6248843, -88.8612177 13.6248757, -88.8612362 13.6248714, -88.8612623 13.6248679, -88.8612849 13.6248662, -88.8613203 13.624763))</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1468026498</t>
+          <t>https://www.openstreetmap.org/way/442688120</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64315064,-88.8688962</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.62483567,-88.86115183</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>geofabrik-way-398066816</t>
+          <t>hot-node-9980784378</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>way/398066816</t>
+          <t>node/9980784378</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hospital Nacional Santa Gertrudis</t>
+          <t>Unidad de Salud De Tepetitán</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2041,12 +2051,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2056,7 +2066,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Tepetitán</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2064,66 +2074,76 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Tepetitán</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Medicina general, Pediatría, Odontología</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>13.64089815</t>
+          <t>13.6495641</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-88.78372</t>
+          <t>-88.8330694</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.7846868 13.6403711, -88.7843794 13.6416996, -88.7838966 13.6415679, -88.7838363 13.6417766, -88.7832784 13.6415787, -88.7827679 13.64141, -88.7831202 13.640009, -88.7846868 13.6403711))</t>
+          <t>POINT (-88.8330694 13.6495641)</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/398066816</t>
+          <t>https://www.openstreetmap.org/node/9980784378</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64089815,-88.78372</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6495641,-88.8330694</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>geofabrik-way-398068809</t>
+          <t>hot-node-5216784308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>way/398068809</t>
+          <t>node/5216784308</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Clínica De Especialidades</t>
+          <t>Clínica Medica Mordagiss</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2138,12 +2158,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2153,7 +2173,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Apastepeque</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2161,66 +2181,76 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Medicina general, Medicina interna</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>13.64218048</t>
+          <t>13.6423061</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-88.78424873</t>
+          <t>-88.784235</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.7843012 13.6421694, -88.7842913 13.6422157, -88.7841956 13.6421913, -88.7842069 13.6421453, -88.7843012 13.6421694))</t>
+          <t>POINT (-88.784235 13.6423061)</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/398068809</t>
+          <t>https://www.openstreetmap.org/node/5216784308</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64218048,-88.78424873</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6423061,-88.784235</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>geofabrik-way-398263306</t>
+          <t>hot-node-5216769528</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>way/398263306</t>
+          <t>node/5216769528</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Clínica Medica Familar</t>
+          <t>KatherLab</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2235,12 +2265,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2250,7 +2280,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Apastepeque</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2258,86 +2288,96 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>13.64093045</t>
+          <t>13.642101</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-88.78478773</t>
+          <t>-88.7851365</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.7848879 13.6408924, -88.7848565 13.6410108, -88.7846876 13.6409685, -88.7847189 13.6408501, -88.7848879 13.6408924))</t>
+          <t>POINT (-88.7851365 13.642101)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/398263306</t>
+          <t>https://www.openstreetmap.org/node/5216769528</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64093045,-88.78478773</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.642101,-88.7851365</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>geofabrik-way-398263312</t>
+          <t>hot-node-5777589873</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>way/398263312</t>
+          <t>node/5777589873</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Clínicas Unidas</t>
+          <t>ISSS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Consultorio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>consultorio</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2347,7 +2387,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Apastepeque</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2355,86 +2395,96 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>13.6415358</t>
+          <t>13.6410547</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-88.78466899</t>
+          <t>-88.7818881</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.7847918 13.6415306, -88.7847748 13.6415974, -88.7845487 13.6415437, -88.7845647 13.6414727, -88.7847918 13.6415306))</t>
+          <t>POINT (-88.7818881 13.6410547)</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/398263312</t>
+          <t>https://www.openstreetmap.org/node/5777589873</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6415358,-88.78466899</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6410547,-88.7818881</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>geofabrik-way-398561342</t>
+          <t>hot-node-4098024175</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>way/398561342</t>
+          <t>node/4098024175</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hospital Divino Niño</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2452,1686 +2502,54 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Tecoluca</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>13.64264136</t>
+          <t>13.5411033</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-88.79002662</t>
+          <t>-88.7807217</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.790129 13.6425477, -88.7900898 13.6427634, -88.7899243 13.6427351, -88.7899634 13.6425193, -88.790129 13.6425477))</t>
+          <t>POINT (-88.7807217 13.5411033)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/398561342</t>
+          <t>https://www.openstreetmap.org/node/4098024175</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64264136,-88.79002662</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>geofabrik-way-442688120</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>geofabrik</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>way/442688120</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Unidad de Salud</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Predio</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>predio</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>13.62483567</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-88.86115183</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.8613203 13.624763, -88.8612849 13.6248662, -88.8612623 13.6248679, -88.8612362 13.6248714, -88.8612177 13.6248757, -88.8611982 13.6248843, -88.8611531 13.6249126, -88.8611371 13.6249212, -88.8611181 13.6249273, -88.861092 13.6249333, -88.8610283 13.6249462, -88.8610363 13.624763, -88.8613203 13.624763))</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/442688120</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.62483567,-88.86115183</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>geofabrik-way-632270864</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>geofabrik</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>way/632270864</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Periferica San Vicente</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Predio</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>predio</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>13.64539727</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-88.77790906</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.7780875 13.645409, -88.7778393 13.6455573, -88.7778017 13.6454979, -88.7777306 13.6453856, -88.7779788 13.6452372, -88.7780875 13.645409))</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/632270864</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64539727,-88.77790906</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>geofabrik-node-5216769528</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>geofabrik</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>node/5216769528</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>KatherLab</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>13.642101</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>-88.7851365</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>POINT (-88.7851365 13.642101)</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/5216769528</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.642101,-88.7851365</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>geofabrik-node-5216784308</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>geofabrik</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>node/5216784308</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Clínica Medica Mordagiss</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>13.6423061</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>-88.784235</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>POINT (-88.784235 13.6423061)</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/5216784308</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6423061,-88.784235</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>hot-way-632270864</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>way/632270864</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Periferica San Vicente</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Polígono</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>poligono</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>13.64539727</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>-88.77790906</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.7780875 13.645409, -88.7778393 13.6455573, -88.7778017 13.6454979, -88.7777306 13.6453856, -88.7779788 13.6452372, -88.7780875 13.645409))</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/632270864</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64539727,-88.77790906</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>hot-way-398561342</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>way/398561342</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Hospital Divino Niño</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Polígono</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>poligono</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>13.64264136</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>-88.79002662</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.7900898 13.6427634, -88.790129 13.6425477, -88.7899634 13.6425193, -88.7899243 13.6427351, -88.7900898 13.6427634))</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/398561342</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64264136,-88.79002662</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>hot-way-398068809</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>way/398068809</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Clínica De Especialidades</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Polígono</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>poligono</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>13.64218048</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>-88.78424873</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.7843012 13.6421694, -88.7842069 13.6421453, -88.7841956 13.6421913, -88.7842913 13.6422157, -88.7843012 13.6421694))</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/398068809</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64218048,-88.78424873</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>hot-way-398263312</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>way/398263312</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Clínicas Unidas</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Polígono</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>poligono</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>13.6415358</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>-88.78466899</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.7845647 13.6414727, -88.7845487 13.6415437, -88.7847748 13.6415974, -88.7847918 13.6415306, -88.7845647 13.6414727))</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/398263312</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6415358,-88.78466899</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>hot-way-398263306</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>way/398263306</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Clínica Medica Familar</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Polígono</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>poligono</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>13.64093045</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-88.78478773</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.7846876 13.6409685, -88.7847189 13.6408501, -88.7848879 13.6408924, -88.7848565 13.6410108, -88.7846876 13.6409685))</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/398263306</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64093045,-88.78478773</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>hot-way-398066816</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>way/398066816</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Hospital Nacional Santa Gertrudis</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Polígono</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>poligono</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>13.64089815</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>-88.78372</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.7843794 13.6416996, -88.7838966 13.6415679, -88.7838363 13.6417766, -88.7832784 13.6415787, -88.7827679 13.64141, -88.7831202 13.640009, -88.7846868 13.6403711, -88.7843794 13.6416996))</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/398066816</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64089815,-88.78372</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>hot-way-442688120</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>way/442688120</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Unidad de Salud</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Polígono</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>poligono</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>San Emigdio El Tablón</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>13.62483567</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>-88.86115183</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>centroide_area</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>POLYGON ((-88.8613203 13.624763, -88.8610363 13.624763, -88.8610283 13.6249462, -88.861092 13.6249333, -88.8611181 13.6249273, -88.8611371 13.6249212, -88.8611531 13.6249126, -88.8611982 13.6248843, -88.8612177 13.6248757, -88.8612362 13.6248714, -88.8612623 13.6248679, -88.8612849 13.6248662, -88.8613203 13.624763))</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/442688120</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.62483567,-88.86115183</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>hot-node-9980784378</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>node/9980784378</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Unidad de Salud De Tepetitán</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Tepetitán</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Tepetitán</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Medicina general, Pediatría, Odontología</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>13.6495641</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>-88.8330694</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>POINT (-88.8330694 13.6495641)</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/9980784378</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6495641,-88.8330694</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>hot-node-5216784308</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>node/5216784308</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Clínica Medica Mordagiss</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Medicina general, Medicina interna</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>13.6423061</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-88.784235</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>POINT (-88.784235 13.6423061)</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/5216784308</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6423061,-88.784235</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>hot-node-5216769528</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>node/5216769528</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>KatherLab</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>13.642101</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>-88.7851365</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>POINT (-88.7851365 13.642101)</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/5216769528</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.642101,-88.7851365</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>hot-node-5777589873</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>node/5777589873</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ISSS</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Consultorio</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>consultorio</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Apastepeque</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>13.6410547</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>-88.7818881</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>POINT (-88.7818881 13.6410547)</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/5777589873</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6410547,-88.7818881</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>hot-node-4098024175</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>node/4098024175</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Unidad de Salud</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Tecoluca</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>13.5411033</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-88.7807217</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>POINT (-88.7807217 13.5411033)</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/4098024175</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=13.5411033,-88.7807217</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA36"/>
+  <autoFilter ref="A1:AA20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>